--- a/المنتجات/batch3-merchant-seo.xlsx
+++ b/المنتجات/batch3-merchant-seo.xlsx
@@ -1420,7 +1420,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Natura Camel Rose</t>
+          <t>Camille Rose</t>
         </is>
       </c>
       <c r="H20" t="n">
